--- a/graphs and tables.xlsx
+++ b/graphs and tables.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Henrik Haaland\Desktop\TDT4225 very large\TDT4225-ex-3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{387B80A5-E644-4F4B-BECA-59341E147D63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{513F806F-201A-46B1-B384-6BBA61BBD947}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="5" xr2:uid="{5518F840-99F1-4209-B8B9-1A3F7907080D}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="11" xr2:uid="{5518F840-99F1-4209-B8B9-1A3F7907080D}"/>
   </bookViews>
   <sheets>
     <sheet name="q1" sheetId="1" r:id="rId1"/>
@@ -19,6 +19,12 @@
     <sheet name="q4" sheetId="4" r:id="rId4"/>
     <sheet name="q5" sheetId="5" r:id="rId5"/>
     <sheet name="q6" sheetId="6" r:id="rId6"/>
+    <sheet name="q7" sheetId="7" r:id="rId7"/>
+    <sheet name="q8" sheetId="8" r:id="rId8"/>
+    <sheet name="q9" sheetId="9" r:id="rId9"/>
+    <sheet name="q10" sheetId="10" r:id="rId10"/>
+    <sheet name="EDA" sheetId="11" r:id="rId11"/>
+    <sheet name="schema" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -44,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="259">
   <si>
     <t>Director</t>
   </si>
@@ -449,6 +455,378 @@
   </si>
   <si>
     <t>1910s</t>
+  </si>
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Year</t>
+  </si>
+  <si>
+    <t>Vote average</t>
+  </si>
+  <si>
+    <t>Vote count</t>
+  </si>
+  <si>
+    <t>Drunken Angel</t>
+  </si>
+  <si>
+    <t>7,70</t>
+  </si>
+  <si>
+    <t>The Bad Sleep Well</t>
+  </si>
+  <si>
+    <t>Elevator to the Gallows</t>
+  </si>
+  <si>
+    <t>7,60</t>
+  </si>
+  <si>
+    <t>Frank &amp; Lola</t>
+  </si>
+  <si>
+    <t>5,70</t>
+  </si>
+  <si>
+    <t>Synchronicity</t>
+  </si>
+  <si>
+    <t>Film count</t>
+  </si>
+  <si>
+    <t>Akira Kurosawa</t>
+  </si>
+  <si>
+    <t>Eijirô Tôno</t>
+  </si>
+  <si>
+    <t>8,13</t>
+  </si>
+  <si>
+    <t>Minoru Itô</t>
+  </si>
+  <si>
+    <t>Haruo Suzuki</t>
+  </si>
+  <si>
+    <t>Hank Mann</t>
+  </si>
+  <si>
+    <t>Quentin Tarantino</t>
+  </si>
+  <si>
+    <t>Harvey Keitel</t>
+  </si>
+  <si>
+    <t>8,10</t>
+  </si>
+  <si>
+    <t>Francis Ford Coppola</t>
+  </si>
+  <si>
+    <t>John Cazale</t>
+  </si>
+  <si>
+    <t>Atsushi Watanabe</t>
+  </si>
+  <si>
+    <t>Toranosuke Ogawa</t>
+  </si>
+  <si>
+    <t>Robert Duvall</t>
+  </si>
+  <si>
+    <t>8,08</t>
+  </si>
+  <si>
+    <t>Noriko Honma</t>
+  </si>
+  <si>
+    <t>Daisuke Katô</t>
+  </si>
+  <si>
+    <t>Ichirô Chiba</t>
+  </si>
+  <si>
+    <t>Susumu Fujita</t>
+  </si>
+  <si>
+    <t>8,07</t>
+  </si>
+  <si>
+    <t>Unknown</t>
+  </si>
+  <si>
+    <t>Shôichi Hirose</t>
+  </si>
+  <si>
+    <t>Haruya Sakamoto</t>
+  </si>
+  <si>
+    <t>Isao Kimura</t>
+  </si>
+  <si>
+    <t>8,05</t>
+  </si>
+  <si>
+    <t>Sean Bean</t>
+  </si>
+  <si>
+    <t>8,03</t>
+  </si>
+  <si>
+    <t>Viggo Mortensen</t>
+  </si>
+  <si>
+    <t>John Rhys-Davies</t>
+  </si>
+  <si>
+    <t>Liv Tyler</t>
+  </si>
+  <si>
+    <t>Mean revenue USDm</t>
+  </si>
+  <si>
+    <t>Original language code</t>
+  </si>
+  <si>
+    <t>Example title</t>
+  </si>
+  <si>
+    <t>fr</t>
+  </si>
+  <si>
+    <t>Leon: The Professional</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>Maria Full of Grace</t>
+  </si>
+  <si>
+    <t>it</t>
+  </si>
+  <si>
+    <t>Once Upon a Time in the West</t>
+  </si>
+  <si>
+    <t>de</t>
+  </si>
+  <si>
+    <t>Bagdad Cafe</t>
+  </si>
+  <si>
+    <t>ja</t>
+  </si>
+  <si>
+    <t>Brother</t>
+  </si>
+  <si>
+    <t>pt</t>
+  </si>
+  <si>
+    <t>A Civil Action</t>
+  </si>
+  <si>
+    <t>xx</t>
+  </si>
+  <si>
+    <t>The Adventures of André and Wally B.</t>
+  </si>
+  <si>
+    <t>nl</t>
+  </si>
+  <si>
+    <t>The Secrets of Jonathan Sperry</t>
+  </si>
+  <si>
+    <t>ru</t>
+  </si>
+  <si>
+    <t>Dirty Deeds</t>
+  </si>
+  <si>
+    <t>zh</t>
+  </si>
+  <si>
+    <t>Crouching Tiger, Hidden Dragon</t>
+  </si>
+  <si>
+    <t>User ID</t>
+  </si>
+  <si>
+    <t>Rating count</t>
+  </si>
+  <si>
+    <t>Population variance</t>
+  </si>
+  <si>
+    <t>0,4114</t>
+  </si>
+  <si>
+    <t>0,4696</t>
+  </si>
+  <si>
+    <t>0,5000</t>
+  </si>
+  <si>
+    <t>0,7207</t>
+  </si>
+  <si>
+    <t>0,7645</t>
+  </si>
+  <si>
+    <t>0,3780</t>
+  </si>
+  <si>
+    <t>Top 10 users by genre diversity</t>
+  </si>
+  <si>
+    <t>Top 10 users by population variance in ratings</t>
+  </si>
+  <si>
+    <t>Measure</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Source movie rows</t>
+  </si>
+  <si>
+    <t>Invalid movie IDs</t>
+  </si>
+  <si>
+    <t>Extra duplicate movie rows</t>
+  </si>
+  <si>
+    <t>Retained movies</t>
+  </si>
+  <si>
+    <t>Source ratings</t>
+  </si>
+  <si>
+    <t>Accepted ratings</t>
+  </si>
+  <si>
+    <t>Rejected ratings</t>
+  </si>
+  <si>
+    <t>Users with accepted ratings</t>
+  </si>
+  <si>
+    <t>Ratings without movie metadata</t>
+  </si>
+  <si>
+    <t>EDA summary (full ratings)</t>
+  </si>
+  <si>
+    <t>Field</t>
+  </si>
+  <si>
+    <t>Movies</t>
+  </si>
+  <si>
+    <t>Share</t>
+  </si>
+  <si>
+    <t>budget</t>
+  </si>
+  <si>
+    <t>revenue</t>
+  </si>
+  <si>
+    <t>tagline</t>
+  </si>
+  <si>
+    <t>genres</t>
+  </si>
+  <si>
+    <t>cast</t>
+  </si>
+  <si>
+    <t>directors</t>
+  </si>
+  <si>
+    <t>runtime</t>
+  </si>
+  <si>
+    <t>release_date</t>
+  </si>
+  <si>
+    <t>Missing or unusable values after cleaning (retained movies)</t>
+  </si>
+  <si>
+    <t>Aditional</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Median positive runtime (minutes)</t>
+  </si>
+  <si>
+    <t>Movies with positive runtime</t>
+  </si>
+  <si>
+    <t>Movies with positive revenue</t>
+  </si>
+  <si>
+    <t>Most common genres</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Thriller</t>
+  </si>
+  <si>
+    <t>Romance</t>
+  </si>
+  <si>
+    <t>movies</t>
+  </si>
+  <si>
+    <t>ratings</t>
+  </si>
+  <si>
+    <t>45 433 movie documents</t>
+  </si>
+  <si>
+    <t>26 024 289 rating documents</t>
+  </si>
+  <si>
+    <t>_id holds the TMDB movie ID</t>
+  </si>
+  <si>
+    <t>_id holds the source row number</t>
+  </si>
+  <si>
+    <t>Movie metadata and numeric attributes</t>
+  </si>
+  <si>
+    <t>user_id and individual rating</t>
+  </si>
+  <si>
+    <t>Embedded genres, cast, directors and keywords</t>
+  </si>
+  <si>
+    <t>rated_at timestamp</t>
+  </si>
+  <si>
+    <t>Embedded production and collection information</t>
+  </si>
+  <si>
+    <t>Original MovieLens movie ID</t>
+  </si>
+  <si>
+    <t>Derived year, decade and primary genre</t>
+  </si>
+  <si>
+    <t>movie_id references movies._id or is null</t>
   </si>
 </sst>
 </file>
@@ -460,10 +838,18 @@
     <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
     <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -490,7 +876,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -513,17 +899,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -537,6 +932,18 @@
     </xf>
     <xf numFmtId="169" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -553,6 +960,1002 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>457200</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>11206</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C0D39C9-D166-F968-071C-37B8C0E65C29}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1205193" y="2800350"/>
+          <a:ext cx="3487831" cy="4449856"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1"/>
+            <a:t>movies</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1"/>
+            <a:t>45,433 movie documents</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400" i="1"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1"/>
+            <a:t>_id  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1"/>
+            <a:t>holds the TMDB movie ID</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400" i="1"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0"/>
+            <a:t>title</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1"/>
+            <a:t>,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t> original_language</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>release_date, release_year, decade runtime, budget, revenue </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>vote_average, vote_count </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>overview, tagline,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>primary_genre</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1"/>
+            <a:t>Embedded arrays</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>genres, cast, directors,</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>keywords production_companies production_countries, spoken_languages</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1"/>
+            <a:t>Embedded object</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400"/>
+            <a:t>belongs_to_collection</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>103094</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>112618</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>569819</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>74518</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="Rectangle: Rounded Corners 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{820F108B-AEDC-4968-AA19-767C61B22FD4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9179859" y="2970118"/>
+          <a:ext cx="3492313" cy="3581400"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>ratings</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>26,024,289 rating documents</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400" i="0">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>_id</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>holds the source row</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t> number</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>user_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>movielens_movie_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>movie_id</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>rating</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="0">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>rated_at</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr lang="en-GB" sz="1400" i="0">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" i="1">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>movie_id stores the mapped TMDB IDor null when no matching movie exists</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163045</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>403412</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>179294</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="5" name="Straight Arrow Connector 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCA5190D-E8E5-02CE-A9C2-B9CA3908C6AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4898091" y="4544545"/>
+          <a:ext cx="3976968" cy="16249"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="76200" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:round/>
+          <a:headEnd type="none" w="med" len="med"/>
+          <a:tailEnd type="arrow" w="med" len="med"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>381001</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>175371</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>560295</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>22411</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="6" name="Rectangle: Rounded Corners 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B6319D57-C233-40B4-A178-B990CF2F73B9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5221942" y="4366371"/>
+          <a:ext cx="3204882" cy="418540"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="en-GB" sz="1400" b="1"/>
+            <a:t>ratings.movie_id references movies._id</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>158565</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>117661</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>587749</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>145676</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="17" name="Group 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F567EF69-72ED-584B-A91D-69B0ADF3B027}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="1368800" y="8118661"/>
+          <a:ext cx="11321302" cy="3647515"/>
+          <a:chOff x="1368800" y="8118661"/>
+          <a:chExt cx="11321302" cy="3647515"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="8" name="Rectangle: Rounded Corners 7">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DACA08AA-F3B9-4DF2-B268-B68039152ACF}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="1368800" y="8118661"/>
+            <a:ext cx="3487831" cy="3647515"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>movies</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:endParaRPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>_id (PK)</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>title</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>release_date</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>revenue</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>vote_average</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:endParaRPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>genres[]</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>cast[]</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>directors[]</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Rectangle: Rounded Corners 8">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1ACE942-F4BB-4609-8C07-F91D1748DE7C}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="9197789" y="8434107"/>
+            <a:ext cx="3492313" cy="2939864"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800" b="1">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>ratings</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:endParaRPr lang="en-GB" sz="1800">
+              <a:solidFill>
+                <a:schemeClr val="lt1"/>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:endParaRPr>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>_id (PK)</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>user_id</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>movie_id (reference)</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>rating</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr algn="ctr" rtl="0"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1800">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:rPr>
+              <a:t>rated_at</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="10" name="Straight Arrow Connector 9">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{305BDEC8-20D6-4EF0-9F80-D45B2FFAD607}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="9" idx="1"/>
+            <a:endCxn id="8" idx="3"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="4856631" y="9904039"/>
+            <a:ext cx="4341158" cy="38380"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln w="76200" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:prstDash val="solid"/>
+            <a:round/>
+            <a:headEnd type="none" w="med" len="med"/>
+            <a:tailEnd type="arrow" w="med" len="med"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:scrgbClr r="0" g="0" b="0"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="11" name="Rectangle: Rounded Corners 10">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3E640EEB-E5C8-4F63-9AA4-14848547B5E5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="5576049" y="9718301"/>
+            <a:ext cx="3204882" cy="418540"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="15000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="en-GB" sz="1400" b="1"/>
+              <a:t>movie_id references movies._id</a:t>
+            </a:r>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1070,6 +2473,721 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8282D6E2-C95D-4984-B76A-DB35E5FA625C}">
+  <dimension ref="B2:J25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="5" width="16.7109375" customWidth="1"/>
+    <col min="7" max="10" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+    </row>
+    <row r="3" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>229</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1282</v>
+      </c>
+      <c r="D4" s="4">
+        <v>20</v>
+      </c>
+      <c r="E4" s="2">
+        <v>11774</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5" s="2">
+        <v>231</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1352</v>
+      </c>
+      <c r="D5" s="4">
+        <v>20</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>567</v>
+      </c>
+      <c r="C6" s="2">
+        <v>972</v>
+      </c>
+      <c r="D6" s="4">
+        <v>20</v>
+      </c>
+      <c r="E6" s="2">
+        <v>12992</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="2">
+        <v>741</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2811</v>
+      </c>
+      <c r="D7" s="4">
+        <v>20</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>836</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1521</v>
+      </c>
+      <c r="D8" s="4">
+        <v>20</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="2">
+        <v>924</v>
+      </c>
+      <c r="C9" s="2">
+        <v>969</v>
+      </c>
+      <c r="D9" s="4">
+        <v>20</v>
+      </c>
+      <c r="E9" s="2">
+        <v>10042</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>1104</v>
+      </c>
+      <c r="C10" s="2">
+        <v>1057</v>
+      </c>
+      <c r="D10" s="4">
+        <v>20</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="2">
+        <v>1145</v>
+      </c>
+      <c r="C11" s="2">
+        <v>553</v>
+      </c>
+      <c r="D11" s="4">
+        <v>20</v>
+      </c>
+      <c r="E11" s="2">
+        <v>13280</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>1214</v>
+      </c>
+      <c r="C12" s="2">
+        <v>165</v>
+      </c>
+      <c r="D12" s="4">
+        <v>20</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="2">
+        <v>1380</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1122</v>
+      </c>
+      <c r="D13" s="4">
+        <v>20</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G14" s="9" t="s">
+        <v>211</v>
+      </c>
+      <c r="H14" s="9"/>
+      <c r="I14" s="9"/>
+      <c r="J14" s="9"/>
+    </row>
+    <row r="15" spans="2:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="G15" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G16" s="2">
+        <v>18703</v>
+      </c>
+      <c r="H16" s="2">
+        <v>20</v>
+      </c>
+      <c r="I16" s="4">
+        <v>13</v>
+      </c>
+      <c r="J16" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="17" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G17" s="2">
+        <v>57842</v>
+      </c>
+      <c r="H17" s="2">
+        <v>20</v>
+      </c>
+      <c r="I17" s="4">
+        <v>14</v>
+      </c>
+      <c r="J17" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="18" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G18" s="2">
+        <v>83102</v>
+      </c>
+      <c r="H18" s="2">
+        <v>20</v>
+      </c>
+      <c r="I18" s="4">
+        <v>15</v>
+      </c>
+      <c r="J18" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="19" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G19" s="2">
+        <v>153882</v>
+      </c>
+      <c r="H19" s="2">
+        <v>20</v>
+      </c>
+      <c r="I19" s="4">
+        <v>15</v>
+      </c>
+      <c r="J19" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="20" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G20" s="2">
+        <v>167241</v>
+      </c>
+      <c r="H20" s="2">
+        <v>34</v>
+      </c>
+      <c r="I20" s="4">
+        <v>14</v>
+      </c>
+      <c r="J20" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="21" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G21" s="2">
+        <v>185889</v>
+      </c>
+      <c r="H21" s="2">
+        <v>26</v>
+      </c>
+      <c r="I21" s="4">
+        <v>14</v>
+      </c>
+      <c r="J21" s="2">
+        <v>50625</v>
+      </c>
+    </row>
+    <row r="22" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G22" s="2">
+        <v>15395</v>
+      </c>
+      <c r="H22" s="2">
+        <v>83</v>
+      </c>
+      <c r="I22" s="4">
+        <v>14</v>
+      </c>
+      <c r="J22" s="2">
+        <v>50618</v>
+      </c>
+    </row>
+    <row r="23" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G23" s="2">
+        <v>71009</v>
+      </c>
+      <c r="H23" s="2">
+        <v>27</v>
+      </c>
+      <c r="I23" s="4">
+        <v>13</v>
+      </c>
+      <c r="J23" s="2">
+        <v>50556</v>
+      </c>
+    </row>
+    <row r="24" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G24" s="2">
+        <v>179759</v>
+      </c>
+      <c r="H24" s="2">
+        <v>21</v>
+      </c>
+      <c r="I24" s="4">
+        <v>13</v>
+      </c>
+      <c r="J24" s="2">
+        <v>50510</v>
+      </c>
+    </row>
+    <row r="25" spans="7:10" x14ac:dyDescent="0.25">
+      <c r="G25" s="2">
+        <v>221535</v>
+      </c>
+      <c r="H25" s="2">
+        <v>120</v>
+      </c>
+      <c r="I25" s="4">
+        <v>19</v>
+      </c>
+      <c r="J25" s="2">
+        <v>50400</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="G14:J14"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C03D692-F4D5-431B-8472-76A6694FED33}">
+  <dimension ref="B2:M41"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="28.7109375" customWidth="1"/>
+    <col min="5" max="7" width="12.7109375" customWidth="1"/>
+    <col min="9" max="10" width="22.7109375" customWidth="1"/>
+    <col min="12" max="13" width="10.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="4" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="2">
+        <v>45466</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="C5" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C6" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="C7" s="2">
+        <v>45433</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="C8" s="2">
+        <v>26024289</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="2">
+        <v>26024289</v>
+      </c>
+    </row>
+    <row r="10" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="C10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="C11" s="2">
+        <v>270896</v>
+      </c>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="C12" s="2">
+        <v>42707</v>
+      </c>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E15" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="F15" s="9"/>
+      <c r="G15" s="10"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="E16" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="F17" s="2">
+        <v>36553</v>
+      </c>
+      <c r="G17" s="2">
+        <v>0.80500000000000005</v>
+      </c>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E18" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F18" s="2">
+        <v>38035</v>
+      </c>
+      <c r="G18" s="2">
+        <v>0.83699999999999997</v>
+      </c>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E19" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F19" s="2">
+        <v>25033</v>
+      </c>
+      <c r="G19" s="2">
+        <v>0.55100000000000005</v>
+      </c>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E20" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="F20" s="2">
+        <v>2442</v>
+      </c>
+      <c r="G20" s="2">
+        <v>5.3999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E21" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F21" s="2">
+        <v>2415</v>
+      </c>
+      <c r="G21" s="2">
+        <v>5.2999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E22" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="F22" s="2">
+        <v>888</v>
+      </c>
+      <c r="G22" s="2">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E23" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="F23" s="2">
+        <v>1818</v>
+      </c>
+      <c r="G23" s="2">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="24" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="E24" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F24" s="2">
+        <v>87</v>
+      </c>
+      <c r="G24" s="2">
+        <v>2E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="I28" s="9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J28" s="9"/>
+    </row>
+    <row r="29" spans="5:10" x14ac:dyDescent="0.25">
+      <c r="I29" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="5:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="I30" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="J30" s="11">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="5:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I31" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="J31" s="11">
+        <v>43615</v>
+      </c>
+    </row>
+    <row r="32" spans="5:10" ht="30" x14ac:dyDescent="0.25">
+      <c r="I32" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="J32" s="11">
+        <v>7398</v>
+      </c>
+    </row>
+    <row r="35" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L35" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="M35" s="9"/>
+    </row>
+    <row r="36" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L36" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="37" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L37" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="M37" s="11">
+        <v>20244</v>
+      </c>
+    </row>
+    <row r="38" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L38" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="M38" s="2">
+        <v>13176</v>
+      </c>
+    </row>
+    <row r="39" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L39" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M39" s="2">
+        <v>7619</v>
+      </c>
+    </row>
+    <row r="40" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L40" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="M40" s="2">
+        <v>6730</v>
+      </c>
+    </row>
+    <row r="41" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L41" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="M41" s="2">
+        <v>6592</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="L35:M35"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{816DCE5C-5C2B-4624-B2FC-CE55D34EF907}">
+  <dimension ref="B3:C9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C3" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C5" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" t="s">
+        <v>251</v>
+      </c>
+      <c r="C6" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="7" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B7" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>255</v>
+      </c>
+      <c r="C8" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" t="s">
+        <v>258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0E73FD-42B2-44D8-9942-2552A781A32E}">
   <dimension ref="B2:E12"/>
@@ -1949,4 +4067,613 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68EFCAC5-8622-4FD0-BCC9-1DCD678327AF}">
+  <dimension ref="B2:E7"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="5" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="2">
+        <v>1948</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1960</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="E4" s="2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1958</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="E5" s="2">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="2">
+        <v>2016</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E6" s="2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C7" s="2">
+        <v>2015</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="E7" s="2">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B30AB68-4A78-46BD-8B3A-1C6620048F7D}">
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="6" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1">
+        <v>1000000</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="4">
+        <v>3</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F3" s="8">
+        <v>0.271841</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D4" s="4">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F4" s="8">
+        <v>0.271841</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D5" s="4">
+        <v>3</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F5" s="8">
+        <v>0.271841</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D6" s="4">
+        <v>3</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F6" s="8">
+        <v>6.5063936699999996</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="4">
+        <v>3</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="8">
+        <v>182.57360633000002</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="4">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="8">
+        <v>99.009750670000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="4">
+        <v>3</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="8">
+        <v>0.16354050000000001</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D10" s="4">
+        <v>3</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="8">
+        <v>0.16354050000000001</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="4">
+        <v>4</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F11" s="8">
+        <v>96.622408250000007</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F12" s="8">
+        <v>0.14121633</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B13" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="D13" s="4">
+        <v>4</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F13" s="8">
+        <v>0.14121633</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B14" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D14" s="4">
+        <v>4</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F14" s="8">
+        <v>0.16354050000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B15" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="D15" s="4">
+        <v>3</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F15" s="8" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B16" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="D16" s="4">
+        <v>3</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F16" s="8">
+        <v>0.271841</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B17" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="D17" s="4">
+        <v>3</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F17" s="8">
+        <v>0.271841</v>
+      </c>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="D18" s="4">
+        <v>4</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="F18" s="8">
+        <v>0.16354050000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B19" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" s="4">
+        <v>3</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F19" s="8">
+        <v>972.18158100000005</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B20" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="D20" s="4">
+        <v>3</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F20" s="8">
+        <v>972.18158100000005</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B21" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="D21" s="4">
+        <v>3</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F21" s="8">
+        <v>972.18158100000005</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B22" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="4">
+        <v>3</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F22" s="8">
+        <v>972.18158100000005</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9630B929-0032-4C9C-81D6-CCD9415D417B}">
+  <dimension ref="B2:D12"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="3" width="16.7109375" customWidth="1"/>
+    <col min="4" max="4" width="35.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" ht="45" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C3" s="2">
+        <v>112</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C4" s="2">
+        <v>72</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="2">
+        <v>56</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="C6" s="2">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="2">
+        <v>30</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="2">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C9" s="2">
+        <v>14</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C10" s="2">
+        <v>12</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C11" s="2">
+        <v>11</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C12" s="2">
+        <v>11</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>